--- a/KURIKULUM2026_REVISI/025_REKOMENDASI_PENGEMBANGAN_MK_PEMINATAN_DAN_CROSS_TRACK_2027.xlsx
+++ b/KURIKULUM2026_REVISI/025_REKOMENDASI_PENGEMBANGAN_MK_PEMINATAN_DAN_CROSS_TRACK_2027.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>`STI-521` IoT, `STI-626` DL</t>
+          <t>`STI-521` IoT, `STI-726` DL</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>`STI-626` DL, `STI-417` Cloud</t>
+          <t>`STI-726` DL, `STI-417` Cloud</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>`STI-414` NLP, `STI-626` DL</t>
+          <t>`STI-414` NLP, `STI-726` DL</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>`STI-414` NLP, `STI-626` DL</t>
+          <t>`STI-414` NLP, `STI-726` DL</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>`STB-501` NetSec, `STI-626`</t>
+          <t>`STB-501` NetSec, `STI-726`</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>`STI-416` Web Back, `STI-627`</t>
+          <t>`STI-416` Web Back, `STI-727`</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>`STI-627` Digital Platform</t>
+          <t>`STI-727` Digital Platform</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
